--- a/src/main/java/com/mycompany/ocxrst/BASES/FORMAPAGO.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/FORMAPAGO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820EB88D-93BE-485A-8351-E6A5CB302872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72BAF0E-9FE2-4C77-AE3C-70E670372750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3670" yWindow="2630" windowWidth="14400" windowHeight="8170" xr2:uid="{F9A238D3-83AF-4EDC-9D53-A9684E4EB159}"/>
+    <workbookView xWindow="3120" yWindow="1200" windowWidth="14400" windowHeight="8170" xr2:uid="{F9A238D3-83AF-4EDC-9D53-A9684E4EB159}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMASDEPAGO" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Forma de pago</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Transferencia Electrónica</t>
+  </si>
+  <si>
+    <t>** Selecciona una opción **</t>
   </si>
 </sst>
 </file>
@@ -100,13 +103,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB044E9-4FF7-4BEC-8DBC-3220344C5E60}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.08984375" customWidth="1"/>
@@ -456,40 +462,46 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
